--- a/snapshots/qc_snapshot.xlsx
+++ b/snapshots/qc_snapshot.xlsx
@@ -1854,7 +1854,9 @@
       <c r="D23" t="n">
         <v>1100002</v>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>479262</v>
+      </c>
       <c r="F23" t="n">
         <v>119</v>
       </c>
@@ -1914,7 +1916,9 @@
       <c r="D24" t="n">
         <v>948789</v>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>473730</v>
+      </c>
       <c r="F24" t="n">
         <v>104</v>
       </c>
@@ -1974,7 +1978,9 @@
       <c r="D25" t="n">
         <v>979258</v>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>419439</v>
+      </c>
       <c r="F25" t="n">
         <v>102</v>
       </c>
@@ -2034,7 +2040,9 @@
       <c r="D26" t="n">
         <v>985310</v>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>390215</v>
+      </c>
       <c r="F26" t="n">
         <v>97</v>
       </c>
@@ -2056,7 +2064,9 @@
       <c r="L26" t="n">
         <v>289668</v>
       </c>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>74850</v>
+      </c>
       <c r="N26" t="n">
         <v>109</v>
       </c>
@@ -2102,7 +2112,9 @@
       <c r="H27" t="n">
         <v>111185</v>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>25022</v>
+      </c>
       <c r="J27" t="n">
         <v>321</v>
       </c>
@@ -2112,7 +2124,9 @@
       <c r="L27" t="n">
         <v>307589</v>
       </c>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>133402</v>
+      </c>
       <c r="N27" t="n">
         <v>102</v>
       </c>
@@ -2158,7 +2172,9 @@
       <c r="H28" t="n">
         <v>119490</v>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>41603</v>
+      </c>
       <c r="J28" t="n">
         <v>335</v>
       </c>
@@ -2168,7 +2184,9 @@
       <c r="L28" t="n">
         <v>329605</v>
       </c>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>146268</v>
+      </c>
       <c r="N28" t="n">
         <v>123</v>
       </c>
@@ -2195,30 +2213,58 @@
       <c r="A29" s="1" t="n">
         <v>46230</v>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="B29" t="n">
+        <v>889</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1101834</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1059961</v>
+      </c>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>129</v>
+      </c>
+      <c r="G29" t="n">
+        <v>164556</v>
+      </c>
+      <c r="H29" t="n">
+        <v>124893</v>
+      </c>
+      <c r="I29" t="n">
+        <v>10459</v>
+      </c>
+      <c r="J29" t="n">
+        <v>273</v>
+      </c>
+      <c r="K29" t="n">
+        <v>286622</v>
+      </c>
+      <c r="L29" t="n">
+        <v>306347</v>
+      </c>
+      <c r="M29" t="n">
+        <v>142063</v>
+      </c>
+      <c r="N29" t="n">
+        <v>104</v>
+      </c>
+      <c r="O29" t="n">
+        <v>100461</v>
+      </c>
+      <c r="P29" t="n">
+        <v>128209</v>
+      </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1395</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1653473</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1619410</v>
       </c>
     </row>
     <row r="30">
@@ -2348,129 +2394,131 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25266</v>
+        <v>26155</v>
       </c>
       <c r="C34" t="n">
-        <v>31969737</v>
+        <v>33071571</v>
       </c>
       <c r="D34" t="n">
-        <v>26555348</v>
+        <v>27615309</v>
       </c>
       <c r="E34" t="n">
-        <v>10102509</v>
+        <v>11865155</v>
       </c>
       <c r="F34" t="n">
-        <v>3500</v>
+        <v>3629</v>
       </c>
       <c r="G34" t="n">
-        <v>4208735</v>
+        <v>4373291</v>
       </c>
       <c r="H34" t="n">
-        <v>2988177</v>
+        <v>3113070</v>
       </c>
       <c r="I34" t="n">
-        <v>1449649</v>
+        <v>1526733</v>
       </c>
       <c r="J34" t="n">
-        <v>7339</v>
+        <v>7612</v>
       </c>
       <c r="K34" t="n">
-        <v>8097212</v>
+        <v>8383834</v>
       </c>
       <c r="L34" t="n">
-        <v>8272035</v>
+        <v>8578382</v>
       </c>
       <c r="M34" t="n">
-        <v>1887292</v>
+        <v>2383875</v>
       </c>
       <c r="N34" t="n">
-        <v>3267</v>
+        <v>3371</v>
       </c>
       <c r="O34" t="n">
-        <v>3282722</v>
+        <v>3383183</v>
       </c>
       <c r="P34" t="n">
-        <v>2664296</v>
+        <v>2792505</v>
       </c>
       <c r="Q34" t="n">
         <v>1599320</v>
       </c>
       <c r="R34" t="n">
-        <v>39372</v>
+        <v>40767</v>
       </c>
       <c r="S34" t="n">
-        <v>47558406</v>
+        <v>49211879</v>
       </c>
       <c r="T34" t="n">
-        <v>40479856</v>
+        <v>42099266</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>0.2038907191123988</v>
+        <v>0.1975810591147106</v>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>0.3587720401912567</v>
+      </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>0.4084624170522697</v>
+        <v>0.4048161461194255</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>0.344438174415828</v>
+        <v>0.3491039128198878</v>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="n">
-        <v>-0.0211342190887732</v>
+        <v>-0.02267886881232382</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
-        <v>0.2330792376437717</v>
+        <v>0.2843418655474333</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
-        <v>0.2321161012139792</v>
+        <v>0.2115226293238508</v>
       </c>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="n">
-        <v>0.4871932499919274</v>
+        <v>0.4727264236075908</v>
       </c>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>0.1748659876655688</v>
+        <v>0.1689486225246777</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>38117763.34615385</v>
+        <v>39431488.5</v>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>5018107.115384615</v>
+        <v>5021185.962962963</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="n">
-        <v>9654368.153846154</v>
+        <v>9996109.76923077</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="n">
-        <v>3914014.692307692</v>
+        <v>4033795.115384615</v>
       </c>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>56704253.3076923</v>
+        <v>58482579.34757835</v>
       </c>
     </row>
     <row r="39">
@@ -2489,7 +2537,7 @@
         <v>198568</v>
       </c>
       <c r="M39" t="n">
-        <v>0.02452300866026479</v>
+        <v>0.02368462925196277</v>
       </c>
     </row>
     <row r="41">

--- a/snapshots/qc_snapshot.xlsx
+++ b/snapshots/qc_snapshot.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T41"/>
+  <dimension ref="A1:T42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2256,7 +2256,9 @@
       <c r="P29" t="n">
         <v>128209</v>
       </c>
-      <c r="Q29" t="inlineStr"/>
+      <c r="Q29" t="n">
+        <v>45222</v>
+      </c>
       <c r="R29" t="n">
         <v>1395</v>
       </c>
@@ -2271,90 +2273,180 @@
       <c r="A30" s="1" t="n">
         <v>46231</v>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="B30" t="n">
+        <v>960</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1153547</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1131926</v>
+      </c>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>119</v>
+      </c>
+      <c r="G30" t="n">
+        <v>154203</v>
+      </c>
+      <c r="H30" t="n">
+        <v>145723</v>
+      </c>
+      <c r="I30" t="n">
+        <v>46082</v>
+      </c>
+      <c r="J30" t="n">
+        <v>271</v>
+      </c>
+      <c r="K30" t="n">
+        <v>296250</v>
+      </c>
+      <c r="L30" t="n">
+        <v>324904</v>
+      </c>
+      <c r="M30" t="n">
+        <v>123111</v>
+      </c>
+      <c r="N30" t="n">
+        <v>81</v>
+      </c>
+      <c r="O30" t="n">
+        <v>87349</v>
+      </c>
+      <c r="P30" t="n">
+        <v>130726</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>46075</v>
+      </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1431</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1691349</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1733279</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
         <v>46232</v>
       </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+      <c r="B31" t="n">
+        <v>1028</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1285906</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1038890</v>
+      </c>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
+      <c r="F31" t="n">
+        <v>156</v>
+      </c>
+      <c r="G31" t="n">
+        <v>189015</v>
+      </c>
+      <c r="H31" t="n">
+        <v>130837</v>
+      </c>
+      <c r="I31" t="n">
+        <v>72860</v>
+      </c>
+      <c r="J31" t="n">
+        <v>322</v>
+      </c>
+      <c r="K31" t="n">
+        <v>351426</v>
+      </c>
+      <c r="L31" t="n">
+        <v>318520</v>
+      </c>
+      <c r="M31" t="n">
+        <v>140664</v>
+      </c>
+      <c r="N31" t="n">
+        <v>102</v>
+      </c>
+      <c r="O31" t="n">
+        <v>101292</v>
+      </c>
+      <c r="P31" t="n">
+        <v>129134</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>52896</v>
+      </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1608</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1927639</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1617381</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
         <v>46233</v>
       </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>988</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1252130</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1089277</v>
+      </c>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>142</v>
+      </c>
+      <c r="G32" t="n">
+        <v>171972</v>
+      </c>
+      <c r="H32" t="n">
+        <v>147334</v>
+      </c>
+      <c r="I32" t="n">
+        <v>54413</v>
+      </c>
+      <c r="J32" t="n">
+        <v>301</v>
+      </c>
+      <c r="K32" t="n">
+        <v>336802</v>
+      </c>
+      <c r="L32" t="n">
+        <v>327340</v>
+      </c>
+      <c r="M32" t="n">
+        <v>154306</v>
+      </c>
+      <c r="N32" t="n">
+        <v>125</v>
+      </c>
+      <c r="O32" t="n">
+        <v>124163</v>
+      </c>
+      <c r="P32" t="n">
+        <v>143445</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>58384</v>
+      </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1556</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1885067</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1707396</v>
       </c>
     </row>
     <row r="33">
@@ -2394,131 +2486,131 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>26155</v>
+        <v>29131</v>
       </c>
       <c r="C34" t="n">
-        <v>33071571</v>
+        <v>36763154</v>
       </c>
       <c r="D34" t="n">
-        <v>27615309</v>
+        <v>30875402</v>
       </c>
       <c r="E34" t="n">
         <v>11865155</v>
       </c>
       <c r="F34" t="n">
-        <v>3629</v>
+        <v>4046</v>
       </c>
       <c r="G34" t="n">
-        <v>4373291</v>
+        <v>4888481</v>
       </c>
       <c r="H34" t="n">
-        <v>3113070</v>
+        <v>3536964</v>
       </c>
       <c r="I34" t="n">
-        <v>1526733</v>
+        <v>1700088</v>
       </c>
       <c r="J34" t="n">
-        <v>7612</v>
+        <v>8506</v>
       </c>
       <c r="K34" t="n">
-        <v>8383834</v>
+        <v>9368312</v>
       </c>
       <c r="L34" t="n">
-        <v>8578382</v>
+        <v>9549146</v>
       </c>
       <c r="M34" t="n">
-        <v>2383875</v>
+        <v>2801956</v>
       </c>
       <c r="N34" t="n">
-        <v>3371</v>
+        <v>3679</v>
       </c>
       <c r="O34" t="n">
-        <v>3383183</v>
+        <v>3695987</v>
       </c>
       <c r="P34" t="n">
-        <v>2792505</v>
+        <v>3195810</v>
       </c>
       <c r="Q34" t="n">
-        <v>1599320</v>
+        <v>1801897</v>
       </c>
       <c r="R34" t="n">
-        <v>40767</v>
+        <v>45362</v>
       </c>
       <c r="S34" t="n">
-        <v>49211879</v>
+        <v>54715934</v>
       </c>
       <c r="T34" t="n">
-        <v>42099266</v>
+        <v>47157322</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>0.1975810591147106</v>
+        <v>0.1906939381712342</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>0.3587720401912567</v>
+        <v>0.3227458394891798</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>0.4048161461194255</v>
+        <v>0.3821121730387982</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>0.3491039128198878</v>
+        <v>0.3477742881684515</v>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="n">
-        <v>-0.02267886881232382</v>
+        <v>-0.01893719082313748</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
-        <v>0.2843418655474333</v>
+        <v>0.2990886725378062</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
-        <v>0.2115226293238508</v>
+        <v>0.1565102430995585</v>
       </c>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="n">
-        <v>0.4727264236075908</v>
+        <v>0.487527959378645</v>
       </c>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>0.1689486225246777</v>
+        <v>0.1602850136400875</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>39431488.5</v>
+        <v>39298543.93103448</v>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>5021185.962962963</v>
+        <v>5225617.620689656</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="n">
-        <v>9996109.76923077</v>
+        <v>10014402.48275862</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="n">
-        <v>4033795.115384615</v>
+        <v>3819186.566666666</v>
       </c>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>58482579.34757835</v>
+        <v>58357750.60114942</v>
       </c>
     </row>
     <row r="39">
@@ -2537,7 +2629,7 @@
         <v>198568</v>
       </c>
       <c r="M39" t="n">
-        <v>0.02368462925196277</v>
+        <v>0.02119570740171762</v>
       </c>
     </row>
     <row r="41">
@@ -2559,6 +2651,17 @@
         <is>
           <t> </t>
         </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="n">
+        <v>0.2438721069572168</v>
       </c>
     </row>
   </sheetData>

--- a/snapshots/qc_snapshot.xlsx
+++ b/snapshots/qc_snapshot.xlsx
@@ -2453,27 +2453,53 @@
       <c r="A33" s="1" t="n">
         <v>46234</v>
       </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="B33" t="n">
+        <v>1187</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1489504</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>193</v>
+      </c>
+      <c r="G33" t="n">
+        <v>231782</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+      <c r="J33" t="n">
+        <v>315</v>
+      </c>
+      <c r="K33" t="n">
+        <v>333386</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
+      <c r="N33" t="n">
+        <v>153</v>
+      </c>
+      <c r="O33" t="n">
+        <v>150360</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>52389</v>
+      </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1848</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2205032</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
@@ -2486,10 +2512,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>29131</v>
+        <v>30318</v>
       </c>
       <c r="C34" t="n">
-        <v>36763154</v>
+        <v>38252658</v>
       </c>
       <c r="D34" t="n">
         <v>30875402</v>
@@ -2498,10 +2524,10 @@
         <v>11865155</v>
       </c>
       <c r="F34" t="n">
-        <v>4046</v>
+        <v>4239</v>
       </c>
       <c r="G34" t="n">
-        <v>4888481</v>
+        <v>5120263</v>
       </c>
       <c r="H34" t="n">
         <v>3536964</v>
@@ -2510,10 +2536,10 @@
         <v>1700088</v>
       </c>
       <c r="J34" t="n">
-        <v>8506</v>
+        <v>8821</v>
       </c>
       <c r="K34" t="n">
-        <v>9368312</v>
+        <v>9701698</v>
       </c>
       <c r="L34" t="n">
         <v>9549146</v>
@@ -2522,22 +2548,22 @@
         <v>2801956</v>
       </c>
       <c r="N34" t="n">
-        <v>3679</v>
+        <v>3832</v>
       </c>
       <c r="O34" t="n">
-        <v>3695987</v>
+        <v>3846347</v>
       </c>
       <c r="P34" t="n">
         <v>3195810</v>
       </c>
       <c r="Q34" t="n">
-        <v>1801897</v>
+        <v>1854286</v>
       </c>
       <c r="R34" t="n">
-        <v>45362</v>
+        <v>47210</v>
       </c>
       <c r="S34" t="n">
-        <v>54715934</v>
+        <v>56920966</v>
       </c>
       <c r="T34" t="n">
         <v>47157322</v>
@@ -2547,70 +2573,70 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>0.1906939381712342</v>
+        <v>0.2389363545776667</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>0.3227458394891798</v>
+        <v>0.3101785763488644</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>0.3821121730387982</v>
+        <v>0.4476435157383564</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>0.3477742881684515</v>
+        <v>0.3320313819817459</v>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="n">
-        <v>-0.01893719082313748</v>
+        <v>0.01597546000448627</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
-        <v>0.2990886725378062</v>
+        <v>0.2888108865066713</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
-        <v>0.1565102430995585</v>
+        <v>0.2035593480213154</v>
       </c>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="n">
-        <v>0.487527959378645</v>
+        <v>0.4820901494326955</v>
       </c>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>0.1602850136400875</v>
+        <v>0.2070440726044621</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>39298543.93103448</v>
+        <v>38252658</v>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>5225617.620689656</v>
+        <v>5120263</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="n">
-        <v>10014402.48275862</v>
+        <v>9701698</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="n">
-        <v>3819186.566666666</v>
+        <v>3846347</v>
       </c>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>58357750.60114942</v>
+        <v>56920966</v>
       </c>
     </row>
     <row r="39">
@@ -2629,7 +2655,7 @@
         <v>198568</v>
       </c>
       <c r="M39" t="n">
-        <v>0.02119570740171762</v>
+        <v>0.0204673449946597</v>
       </c>
     </row>
     <row r="41">
@@ -2661,7 +2687,7 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>0.2438721069572168</v>
+        <v>0.269466041099842</v>
       </c>
     </row>
   </sheetData>
